--- a/public/planilhas/paletes.xlsx
+++ b/public/planilhas/paletes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54C7A178-D8D1-4604-80AD-3A275030C05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B317D3-8C26-4093-8C70-5FF1DC793AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{440AEBC8-16EE-46B1-86C8-B47C6D9C60AC}"/>
   </bookViews>
